--- a/index3/data.xlsx
+++ b/index3/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mibsi\OneDrive\Desktop\index\index2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mibsi\OneDrive\Desktop\index\index3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B5D0A3-9130-4BB6-96D2-65E0F01243E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B77824-EEEE-475D-91DE-1A9420CC1825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7125" yWindow="8265" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>logo</t>
   </si>
@@ -36,31 +36,45 @@
     <t>company</t>
   </si>
   <si>
-    <t>salary</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
     <t>location</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/a/a6/Logo_NIKE.svg</t>
   </si>
   <si>
-    <t>Software Engineer</t>
-  </si>
-  <si>
-    <t>Nike</t>
-  </si>
-  <si>
-    <t>900-1200</t>
-  </si>
-  <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>Downtown,NY</t>
+  </si>
+  <si>
+    <t>jd</t>
+  </si>
+  <si>
+    <t>requirement</t>
+  </si>
+  <si>
+    <t>experience</t>
+  </si>
+  <si>
+    <t>Digital Marketer</t>
+  </si>
+  <si>
+    <t>Creative Agency</t>
+  </si>
+  <si>
+    <t>It is a long established fact that a reader will beff distracted by vbthe creadable content of a page when looking at its layout. The pointf of using Lorem Ipsum is that it has ahf mcore or-lgess normal distribution of letters, as opposed to using, Content here content here making it look like readable.</t>
+  </si>
+  <si>
+    <t>∙ System Software Development
+∙ Mobile Applicationin iOS/Android/Tizen or other platform
+∙ Research and code , libraries, APIs and frameworks
+∙ Strong knowledge on software development life cycle
+∙ Strong problem solving and debugging skills</t>
+  </si>
+  <si>
+    <t>∙ 3 or more years of professional design experience
+∙ Direct response email experience
+∙ Ecommerce website design experience
+∙ Familiarity with mobile and web apps preferred
+∙ Experience using Invision a plus</t>
   </si>
 </sst>
 </file>
@@ -105,13 +119,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -394,14 +411,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.85546875" customWidth="1"/>
     <col min="2" max="2" width="27.85546875" customWidth="1"/>
+    <col min="4" max="4" width="31" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="7" max="7" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -415,33 +436,39 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="240" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
         <v>5</v>
       </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" ht="135" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
     </row>
   </sheetData>

--- a/index3/data.xlsx
+++ b/index3/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mibsi\OneDrive\Desktop\index\index3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B77824-EEEE-475D-91DE-1A9420CC1825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05060EC0-C8A2-4D85-89A2-11DCBCEBA5C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,18 +63,18 @@
     <t>It is a long established fact that a reader will beff distracted by vbthe creadable content of a page when looking at its layout. The pointf of using Lorem Ipsum is that it has ahf mcore or-lgess normal distribution of letters, as opposed to using, Content here content here making it look like readable.</t>
   </si>
   <si>
-    <t>∙ System Software Development
-∙ Mobile Applicationin iOS/Android/Tizen or other platform
-∙ Research and code , libraries, APIs and frameworks
-∙ Strong knowledge on software development life cycle
-∙ Strong problem solving and debugging skills</t>
-  </si>
-  <si>
-    <t>∙ 3 or more years of professional design experience
-∙ Direct response email experience
-∙ Ecommerce website design experience
-∙ Familiarity with mobile and web apps preferred
-∙ Experience using Invision a plus</t>
+    <t>System Software Development
+Mobile Applicationin iOS/Android/Tizen or other platform
+Research and code , libraries, APIs and frameworks
+Strong knowledge on software development life cycle
+Strong problem solving and debugging skills</t>
+  </si>
+  <si>
+    <t>3 or more years of professional design experience
+Direct response email experience
+Ecommerce website design experience
+Familiarity with mobile and web apps preferred
+Experience using Invision a plus</t>
   </si>
 </sst>
 </file>
